--- a/outputs/daily/hr_rankings_2026-07-24.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-24.xlsx
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>60.9</v>
+        <v>61</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>28.2</v>
+        <v>29.7</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3953,12 +3953,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 0 HR</t>
+          <t>Last 7 games: 7/22, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -4428,11 +4428,11 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>60.2</v>
+        <v>60</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Longshot</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -4442,11 +4442,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Strong Barrel, Pitcher Vulnerable, Premium Lineup Spot</t>
+          <t>Strong Barrel, Pitcher Vulnerable, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>51.1</v>
+        <v>59.8</v>
       </c>
       <c r="Q15" t="n">
         <v>73.2</v>
@@ -4455,13 +4455,13 @@
         <v>43.1</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>64.3</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>16.6</v>
+        <v>0</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4528,82 +4528,82 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 1/18, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 13.1% barrel, 22.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 13.1% barrel, 22.5 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>lift-pull EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>13.63</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>45.31</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>91.33</t>
+          <t>92.26</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>102.186</t>
+          <t>103.1979</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4498</t>
+          <t>0.4598</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.2014</t>
+          <t>0.2153</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3238</t>
+          <t>0.3554</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>74.46</t>
+          <t>76.71</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>71.12</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>33.18</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>28.22</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1965</t>
+          <t>0.2074</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>60</v>
+        <v>59.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4722,11 +4722,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Strong Barrel, Pitcher Vulnerable, Platoon Edge</t>
+          <t>Strong Barrel, Pitcher Vulnerable, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>59.8</v>
+        <v>51.1</v>
       </c>
       <c r="Q16" t="n">
         <v>73.2</v>
@@ -4735,13 +4735,13 @@
         <v>43.1</v>
       </c>
       <c r="S16" t="n">
-        <v>64.3</v>
+        <v>100</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -4808,82 +4808,82 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 13.1% barrel, 22.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 13.1% barrel, 22.5 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>13.63</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>45.31</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>92.26</t>
+          <t>91.33</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>103.1979</t>
+          <t>102.186</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4598</t>
+          <t>0.4498</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.2153</t>
+          <t>0.2014</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3554</t>
+          <t>0.3238</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>76.71</t>
+          <t>74.46</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>71.12</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>33.18</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>28.22</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.2074</t>
+          <t>0.1965</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -5268,7 +5268,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>59.4</v>
+        <v>59.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>78</v>
       </c>
       <c r="U18" t="n">
-        <v>87</v>
+        <v>93.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -7163,52 +7163,52 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>678554</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Curtis Mead</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-24T22:45:00Z</t>
+          <t>2026-07-24T20:10:00Z</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Eduardo Rodriguez</t>
+          <t>Tomoyuki Sugano</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>593958</t>
+          <t>608372</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -7226,26 +7226,26 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Pitcher Vulnerable, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>37.6</v>
+        <v>39.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>46.9</v>
+        <v>73.2</v>
       </c>
       <c r="R25" t="n">
-        <v>67.7</v>
+        <v>43.1</v>
       </c>
       <c r="S25" t="n">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U25" t="n">
-        <v>81.7</v>
+        <v>22.8</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -7297,142 +7297,142 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/20, 1 HR</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.2% barrel, 15.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 13.1% barrel, 22.5 HR allowed</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>40.47</t>
+          <t>44.88</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>87.99</t>
+          <t>90.75</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>99.8976</t>
+          <t>100.5843</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>0.4305</t>
+          <t>0.4346</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>0.1768</t>
+          <t>0.1796</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>0.342</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>72.74</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>30.27</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>43.54</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>30.72</t>
+          <t>24.69</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>0.2021</t>
+          <t>0.1792</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>36.81</t>
+          <t>43.02</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>88.55</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>0.4548</t>
+          <t>0.5492</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
-          <t>0.1888</t>
+          <t>0.2448</t>
         </is>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>27.26</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr"/>
@@ -7443,56 +7443,56 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>678554</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Curtis Mead</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-24T20:10:00Z</t>
+          <t>2026-07-24T22:45:00Z</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Tomoyuki Sugano</t>
+          <t>Eduardo Rodriguez</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>608372</t>
+          <t>593958</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>58.8</v>
+        <v>58.9</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7506,26 +7506,26 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>39.4</v>
+        <v>37.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>73.2</v>
+        <v>46.9</v>
       </c>
       <c r="R26" t="n">
-        <v>43.1</v>
+        <v>67.7</v>
       </c>
       <c r="S26" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="T26" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U26" t="n">
-        <v>19.9</v>
+        <v>81.7</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -7577,142 +7577,142 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/23, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 13.1% barrel, 22.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 15.9 HR allowed</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>44.88</t>
+          <t>40.47</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>90.75</t>
+          <t>87.99</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>100.5843</t>
+          <t>99.8976</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>0.4346</t>
+          <t>0.4305</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>0.1796</t>
+          <t>0.1768</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>0.342</t>
+          <t>0.338</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>72.74</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>30.27</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>43.54</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>30.72</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.1792</t>
+          <t>0.2021</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>43.02</t>
+          <t>36.81</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>88.55</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>0.5492</t>
+          <t>0.4548</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>0.2448</t>
+          <t>0.1888</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>27.26</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr"/>
@@ -11355,47 +11355,47 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>691016</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tyler Soderstrom</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-25T00:10:00Z</t>
+          <t>2026-07-24T20:10:00Z</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Zebby Matthews</t>
+          <t>Tomoyuki Sugano</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>805673</t>
+          <t>608372</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -11418,62 +11418,58 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Pitcher Vulnerable, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>45.5</v>
+        <v>34.3</v>
       </c>
       <c r="Q40" t="n">
-        <v>57.4</v>
+        <v>73.2</v>
       </c>
       <c r="R40" t="n">
-        <v>27.1</v>
+        <v>43.1</v>
       </c>
       <c r="S40" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T40" t="n">
         <v>80</v>
       </c>
       <c r="U40" t="n">
-        <v>63.1</v>
+        <v>19.5</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11493,134 +11489,142 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.8% barrel, 14.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 13.1% barrel, 22.5 HR allowed</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>46.16</t>
+          <t>43.18</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>90.62</t>
+          <t>89.36</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
         <is>
-          <t>102.0042</t>
+          <t>101.0033</t>
         </is>
       </c>
       <c r="AR40" t="inlineStr">
         <is>
-          <t>0.4367</t>
+          <t>0.3865</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
         <is>
-          <t>0.1792</t>
+          <t>0.1569</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.3083</t>
         </is>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>74.28</t>
+          <t>73.19</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>42.87</t>
+          <t>32.24</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>36.56</t>
+          <t>35.01</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>0.2176</t>
+          <t>0.1579</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>11.79</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>43.02</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
         <is>
-          <t>90.11</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="BD40" t="inlineStr">
         <is>
-          <t>0.4554</t>
+          <t>0.5492</t>
         </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
-          <t>0.1956</t>
+          <t>0.2448</t>
         </is>
       </c>
       <c r="BF40" t="inlineStr">
         <is>
-          <t>29.27</t>
-        </is>
-      </c>
-      <c r="BG40" t="inlineStr"/>
-      <c r="BH40" t="inlineStr"/>
+          <t>30.77</t>
+        </is>
+      </c>
+      <c r="BG40" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI40" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ40" t="inlineStr"/>
@@ -11631,47 +11635,47 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>691016</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Tyler Soderstrom</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-24T20:10:00Z</t>
+          <t>2026-07-25T00:10:00Z</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Tomoyuki Sugano</t>
+          <t>Zebby Matthews</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>608372</t>
+          <t>805673</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -11680,7 +11684,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>56.5</v>
+        <v>56.6</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -11694,58 +11698,62 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>34.3</v>
+        <v>45.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>73.2</v>
+        <v>57.4</v>
       </c>
       <c r="R41" t="n">
-        <v>43.1</v>
+        <v>27.1</v>
       </c>
       <c r="S41" t="n">
-        <v>93.2</v>
+        <v>95.5</v>
       </c>
       <c r="T41" t="n">
         <v>80</v>
       </c>
       <c r="U41" t="n">
-        <v>18.2</v>
+        <v>63.1</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC41" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11765,142 +11773,134 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/29, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 13.1% barrel, 22.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.8% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>10.49</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>43.18</t>
+          <t>46.16</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>89.36</t>
+          <t>90.62</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>101.0033</t>
+          <t>102.0042</t>
         </is>
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>0.3865</t>
+          <t>0.4367</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
         <is>
-          <t>0.1569</t>
+          <t>0.1792</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr">
         <is>
-          <t>0.3083</t>
+          <t>0.341</t>
         </is>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>73.19</t>
+          <t>74.28</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>32.24</t>
+          <t>42.87</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>35.01</t>
+          <t>36.56</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>0.1579</t>
+          <t>0.2176</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>11.79</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>43.02</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>90.11</t>
         </is>
       </c>
       <c r="BD41" t="inlineStr">
         <is>
-          <t>0.5492</t>
+          <t>0.4554</t>
         </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
-          <t>0.2448</t>
+          <t>0.1956</t>
         </is>
       </c>
       <c r="BF41" t="inlineStr">
         <is>
-          <t>30.77</t>
-        </is>
-      </c>
-      <c r="BG41" t="inlineStr">
-        <is>
-          <t>In From CF</t>
-        </is>
-      </c>
-      <c r="BH41" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
+          <t>29.27</t>
+        </is>
+      </c>
+      <c r="BG41" t="inlineStr"/>
+      <c r="BH41" t="inlineStr"/>
       <c r="BI41" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ41" t="inlineStr"/>
@@ -36275,32 +36275,32 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>666160</t>
+          <t>680776</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Mickey Moniak</t>
+          <t>Jarren Duran</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-07-24T20:10:00Z</t>
+          <t>2026-07-24T23:15:00Z</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -36310,17 +36310,17 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Trey Yesavage</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>702056</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L129" t="n">
@@ -36338,26 +36338,26 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P129" t="n">
-        <v>50.9</v>
+        <v>39.4</v>
       </c>
       <c r="Q129" t="n">
-        <v>32.6</v>
+        <v>32</v>
       </c>
       <c r="R129" t="n">
-        <v>43.1</v>
+        <v>65.7</v>
       </c>
       <c r="S129" t="n">
         <v>64.3</v>
       </c>
       <c r="T129" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U129" t="n">
-        <v>43.2</v>
+        <v>1.6</v>
       </c>
       <c r="V129" t="inlineStr">
         <is>
@@ -36392,7 +36392,7 @@
       <c r="AB129" t="inlineStr"/>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr"/>
@@ -36409,142 +36409,142 @@
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 1 HR</t>
+          <t>Last 7 games: 3/23, 0 HR</t>
         </is>
       </c>
       <c r="AL129" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 6.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 5.6 HR allowed</t>
         </is>
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>11.84</t>
+          <t>10.47</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>41.41</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>89.63</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AQ129" t="inlineStr">
         <is>
-          <t>100.5652</t>
+          <t>101.9902</t>
         </is>
       </c>
       <c r="AR129" t="inlineStr">
         <is>
-          <t>0.4543</t>
+          <t>0.3862</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>0.2154</t>
+          <t>0.1529</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr">
         <is>
-          <t>0.3153</t>
+          <t>0.3043</t>
         </is>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>74.22</t>
+          <t>75.01</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>49.18</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>47.78</t>
+          <t>39.67</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.1622</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>90.36</t>
         </is>
       </c>
       <c r="BD129" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3396</t>
         </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>0.1254</t>
         </is>
       </c>
       <c r="BF129" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="BG129" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH129" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI129" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ129" t="inlineStr"/>
@@ -36555,27 +36555,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>680776</t>
+          <t>668715</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Jarren Duran</t>
+          <t>Spencer Steer</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-07-24T23:15:00Z</t>
+          <t>2026-07-25T00:15:00Z</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -36585,17 +36585,17 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Trey Yesavage</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>702056</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -36604,7 +36604,7 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>46.8</v>
+        <v>46.6</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
@@ -36618,26 +36618,26 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P130" t="n">
-        <v>39.4</v>
+        <v>40.2</v>
       </c>
       <c r="Q130" t="n">
-        <v>32</v>
+        <v>39.8</v>
       </c>
       <c r="R130" t="n">
-        <v>65.7</v>
+        <v>42.1</v>
       </c>
       <c r="S130" t="n">
-        <v>64.3</v>
+        <v>76.2</v>
       </c>
       <c r="T130" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U130" t="n">
-        <v>1.6</v>
+        <v>46.4</v>
       </c>
       <c r="V130" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y130" t="inlineStr">
@@ -36689,27 +36689,27 @@
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/23, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL130" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 5.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.0% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM130" t="inlineStr">
@@ -36719,112 +36719,112 @@
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>41.41</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AQ130" t="inlineStr">
         <is>
-          <t>101.9902</t>
+          <t>99.037</t>
         </is>
       </c>
       <c r="AR130" t="inlineStr">
         <is>
-          <t>0.3862</t>
+          <t>0.4289</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
         <is>
-          <t>0.1529</t>
+          <t>0.1896</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr">
         <is>
-          <t>0.3043</t>
+          <t>0.3294</t>
         </is>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>75.01</t>
+          <t>71.04</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>49.18</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>39.67</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>30.02</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>0.1622</t>
+          <t>0.1814</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>45.13</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>90.36</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD130" t="inlineStr">
         <is>
-          <t>0.3396</t>
+          <t>0.3929</t>
         </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
-          <t>0.1254</t>
+          <t>0.1434</t>
         </is>
       </c>
       <c r="BF130" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="BG130" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH130" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI130" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ130" t="inlineStr"/>
@@ -36835,56 +36835,56 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>668715</t>
+          <t>666160</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spencer Steer</t>
+          <t>Mickey Moniak</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-07-25T00:15:00Z</t>
+          <t>2026-07-24T20:10:00Z</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
@@ -36902,22 +36902,22 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>40.2</v>
+        <v>50.9</v>
       </c>
       <c r="Q131" t="n">
-        <v>39.8</v>
+        <v>32.6</v>
       </c>
       <c r="R131" t="n">
-        <v>42.1</v>
+        <v>43.1</v>
       </c>
       <c r="S131" t="n">
-        <v>76.2</v>
+        <v>64.3</v>
       </c>
       <c r="T131" t="n">
         <v>50</v>
       </c>
       <c r="U131" t="n">
-        <v>46.4</v>
+        <v>37.8</v>
       </c>
       <c r="V131" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y131" t="inlineStr">
@@ -36952,7 +36952,7 @@
       <c r="AB131" t="inlineStr"/>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD131" t="inlineStr"/>
@@ -36969,142 +36969,142 @@
       </c>
       <c r="AH131" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL131" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.0% barrel, 11.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.84</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>89.63</t>
         </is>
       </c>
       <c r="AQ131" t="inlineStr">
         <is>
-          <t>99.037</t>
+          <t>100.5652</t>
         </is>
       </c>
       <c r="AR131" t="inlineStr">
         <is>
-          <t>0.4289</t>
+          <t>0.4543</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr">
         <is>
-          <t>0.1896</t>
+          <t>0.2154</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr">
         <is>
-          <t>0.3294</t>
+          <t>0.3153</t>
         </is>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>71.04</t>
+          <t>74.22</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>44.26</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.78</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>0.1814</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>45.13</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="BD131" t="inlineStr">
         <is>
-          <t>0.3929</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
-          <t>0.1434</t>
+          <t>0.121</t>
         </is>
       </c>
       <c r="BF131" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="BG131" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH131" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI131" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ131" t="inlineStr"/>
@@ -41039,47 +41039,47 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>678882</t>
+          <t>687401</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Ceddanne Rafaela</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-07-24T23:15:00Z</t>
+          <t>2026-07-24T20:10:00Z</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Trey Yesavage</t>
+          <t>Tomoyuki Sugano</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>702056</t>
+          <t>608372</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -41102,26 +41102,26 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Pitcher Vulnerable, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P146" t="n">
-        <v>21</v>
+        <v>15.8</v>
       </c>
       <c r="Q146" t="n">
-        <v>32</v>
+        <v>73.2</v>
       </c>
       <c r="R146" t="n">
-        <v>65.7</v>
+        <v>43.1</v>
       </c>
       <c r="S146" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="T146" t="n">
         <v>50</v>
       </c>
       <c r="U146" t="n">
-        <v>41.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="V146" t="inlineStr">
         <is>
@@ -41135,7 +41135,7 @@
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y146" t="inlineStr">
@@ -41173,142 +41173,142 @@
       </c>
       <c r="AH146" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL146" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 5.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 13.1% barrel, 22.5 HR allowed</t>
         </is>
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>34.29</t>
+          <t>34.41</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>86.83</t>
+          <t>87.07</t>
         </is>
       </c>
       <c r="AQ146" t="inlineStr">
         <is>
-          <t>97.7958</t>
+          <t>98.6612</t>
         </is>
       </c>
       <c r="AR146" t="inlineStr">
         <is>
-          <t>0.3691</t>
+          <t>0.3438</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>0.1271</t>
+          <t>0.0981</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr">
         <is>
-          <t>0.2882</t>
+          <t>0.2967</t>
         </is>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>70.16</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>28.11</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>30.16</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>25.51</t>
+          <t>21.36</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>0.1594</t>
+          <t>0.1052</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>43.02</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>90.36</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="BD146" t="inlineStr">
         <is>
-          <t>0.3396</t>
+          <t>0.5492</t>
         </is>
       </c>
       <c r="BE146" t="inlineStr">
         <is>
-          <t>0.1254</t>
+          <t>0.2448</t>
         </is>
       </c>
       <c r="BF146" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="BG146" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH146" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI146" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ146" t="inlineStr"/>
@@ -41319,27 +41319,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>680779</t>
+          <t>678882</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Henry Davis</t>
+          <t>Ceddanne Rafaela</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-07-24T22:40:00Z</t>
+          <t>2026-07-24T23:15:00Z</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -41349,26 +41349,26 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Matthew Boyd</t>
+          <t>Trey Yesavage</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>571510</t>
+          <t>702056</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
@@ -41382,62 +41382,58 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P147" t="n">
-        <v>36.4</v>
+        <v>21</v>
       </c>
       <c r="Q147" t="n">
-        <v>48.3</v>
+        <v>32</v>
       </c>
       <c r="R147" t="n">
-        <v>38.8</v>
+        <v>65.7</v>
       </c>
       <c r="S147" t="n">
-        <v>47.9</v>
+        <v>100</v>
       </c>
       <c r="T147" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U147" t="n">
-        <v>37.8</v>
+        <v>41.7</v>
       </c>
       <c r="V147" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W147" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X147" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y147" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr"/>
       <c r="AC147" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -41457,12 +41453,12 @@
       </c>
       <c r="AH147" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr">
@@ -41472,12 +41468,12 @@
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 1 HR</t>
+          <t>Last 7 games: 8/29, 1 HR</t>
         </is>
       </c>
       <c r="AL147" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.8% barrel, 9.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 5.6 HR allowed</t>
         </is>
       </c>
       <c r="AM147" t="inlineStr">
@@ -41487,112 +41483,112 @@
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>38.94</t>
+          <t>34.29</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>89.37</t>
+          <t>86.83</t>
         </is>
       </c>
       <c r="AQ147" t="inlineStr">
         <is>
-          <t>100.607</t>
+          <t>97.7958</t>
         </is>
       </c>
       <c r="AR147" t="inlineStr">
         <is>
-          <t>0.3561</t>
+          <t>0.3691</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>0.1529</t>
+          <t>0.1271</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr">
         <is>
-          <t>0.2895</t>
+          <t>0.2882</t>
         </is>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>70.16</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>52.05</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>26.84</t>
+          <t>25.51</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>0.1481</t>
+          <t>0.1594</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>43.11</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>89.55</t>
+          <t>90.36</t>
         </is>
       </c>
       <c r="BD147" t="inlineStr">
         <is>
-          <t>0.4281</t>
+          <t>0.3396</t>
         </is>
       </c>
       <c r="BE147" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>0.1254</t>
         </is>
       </c>
       <c r="BF147" t="inlineStr">
         <is>
-          <t>24.73</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="BG147" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH147" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI147" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ147" t="inlineStr"/>
@@ -41603,27 +41599,27 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>672695</t>
+          <t>680779</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Geraldo Perdomo</t>
+          <t>Henry Davis</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-07-24T22:45:00Z</t>
+          <t>2026-07-24T22:40:00Z</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -41633,17 +41629,17 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Carson Palmquist</t>
+          <t>Matthew Boyd</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>687223</t>
+          <t>571510</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -41666,39 +41662,47 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P148" t="n">
-        <v>13.1</v>
+        <v>36.4</v>
       </c>
       <c r="Q148" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="R148" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="S148" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="T148" t="n">
+        <v>78</v>
+      </c>
+      <c r="U148" t="n">
         <v>37.8</v>
       </c>
-      <c r="R148" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="S148" t="n">
-        <v>96.59999999999999</v>
-      </c>
-      <c r="T148" t="n">
-        <v>75</v>
-      </c>
-      <c r="U148" t="n">
-        <v>24.3</v>
-      </c>
       <c r="V148" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W148" t="inlineStr"/>
-      <c r="X148" t="inlineStr"/>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z148" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -41706,12 +41710,12 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>not found on RotoWire</t>
+          <t>lineup projected / unconfirmed</t>
         </is>
       </c>
       <c r="AC148" t="inlineStr">
@@ -41733,12 +41737,12 @@
       </c>
       <c r="AH148" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ148" t="inlineStr">
@@ -41748,12 +41752,12 @@
       </c>
       <c r="AK148" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 1 HR</t>
+          <t>Last 7 games: 5/20, 1 HR</t>
         </is>
       </c>
       <c r="AL148" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.4% barrel, 3.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.8% barrel, 9.9 HR allowed</t>
         </is>
       </c>
       <c r="AM148" t="inlineStr">
@@ -41763,112 +41767,112 @@
       </c>
       <c r="AN148" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>38.94</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>87.18</t>
+          <t>89.37</t>
         </is>
       </c>
       <c r="AQ148" t="inlineStr">
         <is>
-          <t>96.6063</t>
+          <t>100.607</t>
         </is>
       </c>
       <c r="AR148" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>0.3561</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr">
         <is>
-          <t>0.1047</t>
+          <t>0.1529</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>0.2895</t>
         </is>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>67.39</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>44.22</t>
+          <t>52.05</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>26.22</t>
+          <t>26.84</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>0.1335</t>
+          <t>0.1481</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>32.58</t>
+          <t>43.11</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>89.55</t>
         </is>
       </c>
       <c r="BD148" t="inlineStr">
         <is>
-          <t>0.4173</t>
+          <t>0.4281</t>
         </is>
       </c>
       <c r="BE148" t="inlineStr">
         <is>
-          <t>0.1659</t>
+          <t>0.172</t>
         </is>
       </c>
       <c r="BF148" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>24.73</t>
         </is>
       </c>
       <c r="BG148" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH148" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI148" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ148" t="inlineStr"/>
@@ -41879,56 +41883,56 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>672695</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Geraldo Perdomo</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-07-24T20:10:00Z</t>
+          <t>2026-07-24T22:45:00Z</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Tomoyuki Sugano</t>
+          <t>Carson Palmquist</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>608372</t>
+          <t>687223</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="M149" t="inlineStr">
         <is>
@@ -41942,58 +41946,54 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P149" t="n">
-        <v>15.8</v>
+        <v>13.1</v>
       </c>
       <c r="Q149" t="n">
-        <v>73.2</v>
+        <v>37.8</v>
       </c>
       <c r="R149" t="n">
-        <v>43.1</v>
+        <v>67.7</v>
       </c>
       <c r="S149" t="n">
-        <v>52.4</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T149" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U149" t="n">
-        <v>75.8</v>
+        <v>24.3</v>
       </c>
       <c r="V149" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W149" t="inlineStr">
+      <c r="W149" t="inlineStr"/>
+      <c r="X149" t="inlineStr"/>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X149" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y149" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB149" t="inlineStr"/>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC149" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -42013,142 +42013,142 @@
       </c>
       <c r="AH149" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/25, 1 HR</t>
         </is>
       </c>
       <c r="AL149" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 13.1% barrel, 22.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.4% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN149" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>87.07</t>
+          <t>87.18</t>
         </is>
       </c>
       <c r="AQ149" t="inlineStr">
         <is>
-          <t>98.6612</t>
+          <t>96.6063</t>
         </is>
       </c>
       <c r="AR149" t="inlineStr">
         <is>
-          <t>0.3438</t>
+          <t>0.361</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr">
         <is>
-          <t>0.0981</t>
+          <t>0.1047</t>
         </is>
       </c>
       <c r="AT149" t="inlineStr">
         <is>
-          <t>0.2967</t>
+          <t>0.335</t>
         </is>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>67.39</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>28.11</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>30.16</t>
+          <t>44.22</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>26.22</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>0.1052</t>
+          <t>0.1335</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>43.02</t>
+          <t>32.58</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD149" t="inlineStr">
         <is>
-          <t>0.5492</t>
+          <t>0.4173</t>
         </is>
       </c>
       <c r="BE149" t="inlineStr">
         <is>
-          <t>0.2448</t>
+          <t>0.1659</t>
         </is>
       </c>
       <c r="BF149" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="BG149" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH149" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI149" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ149" t="inlineStr"/>
@@ -42159,47 +42159,47 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>694374</t>
+          <t>694249</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Tim Tawa</t>
+          <t>Cole Carrigg</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-07-24T22:45:00Z</t>
+          <t>2026-07-24T20:10:00Z</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Carson Palmquist</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>687223</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -42222,57 +42222,61 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P150" t="n">
-        <v>31.7</v>
+        <v>26.1</v>
       </c>
       <c r="Q150" t="n">
-        <v>38.2</v>
+        <v>32</v>
       </c>
       <c r="R150" t="n">
-        <v>67.7</v>
+        <v>43.1</v>
       </c>
       <c r="S150" t="n">
-        <v>44.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T150" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U150" t="n">
-        <v>36.3</v>
+        <v>36.5</v>
       </c>
       <c r="V150" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W150" t="inlineStr"/>
-      <c r="X150" t="inlineStr"/>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y150" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB150" t="inlineStr"/>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD150" t="inlineStr"/>
@@ -42289,27 +42293,27 @@
       </c>
       <c r="AH150" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL150" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 3.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.8% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM150" t="inlineStr">
@@ -42319,112 +42323,112 @@
       </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>39.51</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>88.71</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AQ150" t="inlineStr">
         <is>
-          <t>99.0963</t>
+          <t>98.267</t>
         </is>
       </c>
       <c r="AR150" t="inlineStr">
         <is>
-          <t>0.3701</t>
+          <t>0.405</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>0.1466</t>
+          <t>0.152</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr">
         <is>
-          <t>0.2949</t>
+          <t>0.327</t>
         </is>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>73.87</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>0.1656</t>
+          <t>0.213</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>32.58</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="BD150" t="inlineStr">
         <is>
-          <t>0.4173</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="BE150" t="inlineStr">
         <is>
-          <t>0.1659</t>
+          <t>0.121</t>
         </is>
       </c>
       <c r="BF150" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="BG150" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH150" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI150" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ150" t="inlineStr"/>
@@ -42435,27 +42439,27 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>694374</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Tim Tawa</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-07-24T23:10:00Z</t>
+          <t>2026-07-24T22:45:00Z</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -42465,17 +42469,17 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Joey Cantillo</t>
+          <t>Carson Palmquist</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>676282</t>
+          <t>687223</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -42502,54 +42506,50 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>40.8</v>
+        <v>31.7</v>
       </c>
       <c r="Q151" t="n">
-        <v>34.1</v>
+        <v>38.2</v>
       </c>
       <c r="R151" t="n">
-        <v>41.1</v>
+        <v>67.7</v>
       </c>
       <c r="S151" t="n">
-        <v>64.3</v>
+        <v>44.8</v>
       </c>
       <c r="T151" t="n">
         <v>78</v>
       </c>
       <c r="U151" t="n">
-        <v>20.8</v>
+        <v>36.3</v>
       </c>
       <c r="V151" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W151" t="inlineStr">
+      <c r="W151" t="inlineStr"/>
+      <c r="X151" t="inlineStr"/>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y151" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB151" t="inlineStr"/>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC151" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -42569,12 +42569,12 @@
       </c>
       <c r="AH151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ151" t="inlineStr">
@@ -42584,12 +42584,12 @@
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/22, 1 HR</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL151" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.5% barrel, 11.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM151" t="inlineStr">
@@ -42599,57 +42599,57 @@
       </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>49.17</t>
+          <t>39.51</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>88.71</t>
         </is>
       </c>
       <c r="AQ151" t="inlineStr">
         <is>
-          <t>102.281</t>
+          <t>99.0963</t>
         </is>
       </c>
       <c r="AR151" t="inlineStr">
         <is>
-          <t>0.3837</t>
+          <t>0.3701</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr">
         <is>
-          <t>0.1492</t>
+          <t>0.1466</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr">
         <is>
-          <t>0.3069</t>
+          <t>0.2949</t>
         </is>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>75.73</t>
+          <t>73.87</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>57.05</t>
+          <t>37.58</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>24.33</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -42659,52 +42659,52 @@
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>0.1414</t>
+          <t>0.1656</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>38.44</t>
+          <t>32.58</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>88.17</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD151" t="inlineStr">
         <is>
-          <t>0.3679</t>
+          <t>0.4173</t>
         </is>
       </c>
       <c r="BE151" t="inlineStr">
         <is>
-          <t>0.1389</t>
+          <t>0.1659</t>
         </is>
       </c>
       <c r="BF151" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="BG151" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH151" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI151" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ151" t="inlineStr"/>
@@ -42715,27 +42715,27 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>657041</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Lane Thomas</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-07-24T22:40:00Z</t>
+          <t>2026-07-24T23:10:00Z</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -42745,17 +42745,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Joey Cantillo</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>676282</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -42764,7 +42764,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
       <c r="M152" t="inlineStr">
         <is>
@@ -42778,26 +42778,26 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P152" t="n">
-        <v>26.5</v>
+        <v>40.8</v>
       </c>
       <c r="Q152" t="n">
-        <v>25.6</v>
+        <v>34.1</v>
       </c>
       <c r="R152" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S152" t="n">
-        <v>100</v>
+        <v>64.3</v>
       </c>
       <c r="T152" t="n">
         <v>78</v>
       </c>
       <c r="U152" t="n">
-        <v>57.6</v>
+        <v>20.8</v>
       </c>
       <c r="V152" t="inlineStr">
         <is>
@@ -42811,7 +42811,7 @@
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
@@ -42849,27 +42849,27 @@
       </c>
       <c r="AH152" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/22, 1 HR</t>
         </is>
       </c>
       <c r="AL152" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 12.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.5% barrel, 11.4 HR allowed</t>
         </is>
       </c>
       <c r="AM152" t="inlineStr">
@@ -42879,112 +42879,112 @@
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>38.72</t>
+          <t>49.17</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>88.99</t>
+          <t>91.49</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
         <is>
-          <t>99.586</t>
+          <t>102.281</t>
         </is>
       </c>
       <c r="AR152" t="inlineStr">
         <is>
-          <t>0.3511</t>
+          <t>0.3837</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>0.1264</t>
+          <t>0.1492</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>0.3004</t>
+          <t>0.3069</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>75.73</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>57.05</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>24.33</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>0.1505</t>
+          <t>0.1414</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>33.77</t>
+          <t>38.44</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>86.66</t>
+          <t>88.17</t>
         </is>
       </c>
       <c r="BD152" t="inlineStr">
         <is>
-          <t>0.3475</t>
+          <t>0.3679</t>
         </is>
       </c>
       <c r="BE152" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1389</t>
         </is>
       </c>
       <c r="BF152" t="inlineStr">
         <is>
-          <t>24.01</t>
+          <t>27.65</t>
         </is>
       </c>
       <c r="BG152" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH152" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI152" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ152" t="inlineStr"/>
@@ -42995,27 +42995,27 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>657757</t>
+          <t>657041</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Gavin Sheets</t>
+          <t>Lane Thomas</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-07-24T23:10:00Z</t>
+          <t>2026-07-24T22:40:00Z</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -43025,22 +43025,22 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Ryan Gusto</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>687473</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L153" t="n">
@@ -43058,26 +43058,26 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P153" t="n">
-        <v>35.1</v>
+        <v>26.5</v>
       </c>
       <c r="Q153" t="n">
-        <v>47.6</v>
+        <v>25.6</v>
       </c>
       <c r="R153" t="n">
-        <v>35</v>
+        <v>40.1</v>
       </c>
       <c r="S153" t="n">
-        <v>64.3</v>
+        <v>100</v>
       </c>
       <c r="T153" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U153" t="n">
-        <v>5.7</v>
+        <v>57.6</v>
       </c>
       <c r="V153" t="inlineStr">
         <is>
@@ -43091,7 +43091,7 @@
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y153" t="inlineStr">
@@ -43129,27 +43129,27 @@
       </c>
       <c r="AH153" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL153" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.2% barrel, 7.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
@@ -43159,112 +43159,112 @@
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>38.72</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.99</t>
         </is>
       </c>
       <c r="AQ153" t="inlineStr">
         <is>
-          <t>99.753</t>
+          <t>99.586</t>
         </is>
       </c>
       <c r="AR153" t="inlineStr">
         <is>
-          <t>0.4089</t>
+          <t>0.3511</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>0.1655</t>
+          <t>0.1264</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr">
         <is>
-          <t>0.3281</t>
+          <t>0.3004</t>
         </is>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>74.52</t>
+          <t>72.49</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>47.77</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>39.12</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>23.21</t>
+          <t>25.58</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>0.1868</t>
+          <t>0.1505</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>43.39</t>
+          <t>33.77</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>89.83</t>
+          <t>86.66</t>
         </is>
       </c>
       <c r="BD153" t="inlineStr">
         <is>
-          <t>0.4285</t>
+          <t>0.3475</t>
         </is>
       </c>
       <c r="BE153" t="inlineStr">
         <is>
-          <t>0.1676</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BF153" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>24.01</t>
         </is>
       </c>
       <c r="BG153" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH153" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI153" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ153" t="inlineStr"/>
@@ -43275,27 +43275,27 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>681082</t>
+          <t>657757</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Gavin Sheets</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-07-24T22:45:00Z</t>
+          <t>2026-07-24T23:10:00Z</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -43305,17 +43305,17 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Ryan Gusto</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>687473</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -43324,7 +43324,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>44.7</v>
+        <v>44.8</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
@@ -43342,22 +43342,22 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>27.5</v>
+        <v>35.1</v>
       </c>
       <c r="Q154" t="n">
-        <v>36.2</v>
+        <v>47.6</v>
       </c>
       <c r="R154" t="n">
-        <v>50.3</v>
+        <v>35</v>
       </c>
       <c r="S154" t="n">
-        <v>76.2</v>
+        <v>64.3</v>
       </c>
       <c r="T154" t="n">
         <v>80</v>
       </c>
       <c r="U154" t="n">
-        <v>30</v>
+        <v>5.7</v>
       </c>
       <c r="V154" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
       </c>
       <c r="X154" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y154" t="inlineStr">
@@ -43409,12 +43409,12 @@
       </c>
       <c r="AH154" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ154" t="inlineStr">
@@ -43424,12 +43424,12 @@
       </c>
       <c r="AK154" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 3/19, 0 HR</t>
         </is>
       </c>
       <c r="AL154" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 7.2 HR allowed</t>
         </is>
       </c>
       <c r="AM154" t="inlineStr">
@@ -43439,112 +43439,112 @@
       </c>
       <c r="AN154" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AQ154" t="inlineStr">
         <is>
-          <t>98.5058</t>
+          <t>99.753</t>
         </is>
       </c>
       <c r="AR154" t="inlineStr">
         <is>
-          <t>0.4042</t>
+          <t>0.4089</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr">
         <is>
-          <t>0.1453</t>
+          <t>0.1655</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr">
         <is>
-          <t>0.3179</t>
+          <t>0.3281</t>
         </is>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>69.82</t>
+          <t>74.52</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>47.77</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>39.12</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>23.21</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>0.1431</t>
+          <t>0.1868</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>9.22</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>43.39</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>89.83</t>
         </is>
       </c>
       <c r="BD154" t="inlineStr">
         <is>
-          <t>0.3623</t>
+          <t>0.4285</t>
         </is>
       </c>
       <c r="BE154" t="inlineStr">
         <is>
-          <t>0.1414</t>
+          <t>0.1676</t>
         </is>
       </c>
       <c r="BF154" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="BG154" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH154" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI154" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ154" t="inlineStr"/>
@@ -43555,56 +43555,56 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>691720</t>
+          <t>681082</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-07-24T20:10:00Z</t>
+          <t>2026-07-24T22:45:00Z</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>44.5</v>
+        <v>44.7</v>
       </c>
       <c r="M155" t="inlineStr">
         <is>
@@ -43618,26 +43618,26 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P155" t="n">
-        <v>25.9</v>
+        <v>27.5</v>
       </c>
       <c r="Q155" t="n">
-        <v>32.6</v>
+        <v>36.2</v>
       </c>
       <c r="R155" t="n">
-        <v>43.1</v>
+        <v>50.3</v>
       </c>
       <c r="S155" t="n">
-        <v>100</v>
+        <v>76.2</v>
       </c>
       <c r="T155" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U155" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="V155" t="inlineStr">
         <is>
@@ -43651,7 +43651,7 @@
       </c>
       <c r="X155" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y155" t="inlineStr">
@@ -43672,7 +43672,7 @@
       <c r="AB155" t="inlineStr"/>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD155" t="inlineStr"/>
@@ -43689,12 +43689,12 @@
       </c>
       <c r="AH155" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ155" t="inlineStr">
@@ -43704,12 +43704,12 @@
       </c>
       <c r="AK155" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/20, 0 HR</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL155" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 6.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM155" t="inlineStr">
@@ -43719,112 +43719,112 @@
       </c>
       <c r="AN155" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>35.52</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>89.16</t>
+          <t>88.65</t>
         </is>
       </c>
       <c r="AQ155" t="inlineStr">
         <is>
-          <t>99.7383</t>
+          <t>98.5058</t>
         </is>
       </c>
       <c r="AR155" t="inlineStr">
         <is>
-          <t>0.3642</t>
+          <t>0.4042</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>0.1236</t>
+          <t>0.1453</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr">
         <is>
-          <t>0.3161</t>
+          <t>0.3179</t>
         </is>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>69.82</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>34.17</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>0.1329</t>
+          <t>0.1431</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>88.23</t>
         </is>
       </c>
       <c r="BD155" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3623</t>
         </is>
       </c>
       <c r="BE155" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>0.1414</t>
         </is>
       </c>
       <c r="BF155" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="BG155" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH155" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI155" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ155" t="inlineStr"/>
@@ -43835,12 +43835,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>694249</t>
+          <t>691720</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Cole Carrigg</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -43865,7 +43865,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -43902,22 +43902,22 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="Q156" t="n">
-        <v>32</v>
+        <v>32.6</v>
       </c>
       <c r="R156" t="n">
         <v>43.1</v>
       </c>
       <c r="S156" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="T156" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U156" t="n">
-        <v>29.7</v>
+        <v>12</v>
       </c>
       <c r="V156" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
       </c>
       <c r="X156" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y156" t="inlineStr">
@@ -43952,7 +43952,7 @@
       <c r="AB156" t="inlineStr"/>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD156" t="inlineStr"/>
@@ -43969,12 +43969,12 @@
       </c>
       <c r="AH156" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ156" t="inlineStr">
@@ -43984,12 +43984,12 @@
       </c>
       <c r="AK156" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/22, 0 HR</t>
+          <t>Last 7 games: 4/20, 0 HR</t>
         </is>
       </c>
       <c r="AL156" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.8% barrel, 6.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM156" t="inlineStr">
@@ -43999,67 +43999,67 @@
       </c>
       <c r="AN156" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>40.42</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.16</t>
         </is>
       </c>
       <c r="AQ156" t="inlineStr">
         <is>
-          <t>98.267</t>
+          <t>99.7383</t>
         </is>
       </c>
       <c r="AR156" t="inlineStr">
         <is>
-          <t>0.405</t>
+          <t>0.3642</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>0.1236</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>0.3161</t>
         </is>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>0.1329</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
@@ -48583,52 +48583,52 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>663698</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Joey Bart</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-07-24T20:10:00Z</t>
+          <t>2026-07-24T23:05:00Z</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Tomoyuki Sugano</t>
+          <t>Trevor Rogers</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>608372</t>
+          <t>669432</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L173" t="n">
@@ -48646,26 +48646,26 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P173" t="n">
-        <v>11.6</v>
+        <v>34.9</v>
       </c>
       <c r="Q173" t="n">
-        <v>73.2</v>
+        <v>36.3</v>
       </c>
       <c r="R173" t="n">
-        <v>43.1</v>
+        <v>47.6</v>
       </c>
       <c r="S173" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T173" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U173" t="n">
-        <v>28.9</v>
+        <v>21.8</v>
       </c>
       <c r="V173" t="inlineStr">
         <is>
@@ -48679,7 +48679,7 @@
       </c>
       <c r="X173" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y173" t="inlineStr">
@@ -48717,142 +48717,142 @@
       </c>
       <c r="AH173" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/16, 0 HR</t>
+          <t>Last 7 games: 2/14, 1 HR</t>
         </is>
       </c>
       <c r="AL173" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 13.1% barrel, 22.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 8.8 HR allowed</t>
         </is>
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>27.73</t>
+          <t>36.27</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>86.86</t>
         </is>
       </c>
       <c r="AQ173" t="inlineStr">
         <is>
-          <t>97.0306</t>
+          <t>99.107</t>
         </is>
       </c>
       <c r="AR173" t="inlineStr">
         <is>
-          <t>0.3015</t>
+          <t>0.3835</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.1751</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2998</t>
         </is>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>69.94</t>
+          <t>75.14</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>50.36</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>34.69</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>31.72</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>0.1056</t>
+          <t>0.1386</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>43.02</t>
+          <t>42.17</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="BD173" t="inlineStr">
         <is>
-          <t>0.5492</t>
+          <t>0.3956</t>
         </is>
       </c>
       <c r="BE173" t="inlineStr">
         <is>
-          <t>0.2448</t>
+          <t>0.1489</t>
         </is>
       </c>
       <c r="BF173" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="BG173" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH173" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI173" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ173" t="inlineStr"/>
@@ -48863,27 +48863,27 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>663698</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Joey Bart</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-07-24T23:05:00Z</t>
+          <t>2026-07-24T23:10:00Z</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -48893,17 +48893,17 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Trevor Rogers</t>
+          <t>Shane McClanahan</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>669432</t>
+          <t>663556</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -48912,7 +48912,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="M174" t="inlineStr">
         <is>
@@ -48926,26 +48926,26 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P174" t="n">
-        <v>34.9</v>
+        <v>14.2</v>
       </c>
       <c r="Q174" t="n">
-        <v>36.3</v>
+        <v>42.1</v>
       </c>
       <c r="R174" t="n">
-        <v>47.6</v>
+        <v>41.1</v>
       </c>
       <c r="S174" t="n">
-        <v>52.4</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T174" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U174" t="n">
-        <v>21.8</v>
+        <v>34.2</v>
       </c>
       <c r="V174" t="inlineStr">
         <is>
@@ -48959,7 +48959,7 @@
       </c>
       <c r="X174" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y174" t="inlineStr">
@@ -48980,7 +48980,7 @@
       <c r="AB174" t="inlineStr"/>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD174" t="inlineStr"/>
@@ -48997,12 +48997,12 @@
       </c>
       <c r="AH174" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ174" t="inlineStr">
@@ -49012,12 +49012,12 @@
       </c>
       <c r="AK174" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/14, 1 HR</t>
+          <t>Last 7 games: 7/31, 1 HR</t>
         </is>
       </c>
       <c r="AL174" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 8.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.9% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AM174" t="inlineStr">
@@ -49027,112 +49027,112 @@
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>36.27</t>
+          <t>33.19</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>86.86</t>
+          <t>86.95</t>
         </is>
       </c>
       <c r="AQ174" t="inlineStr">
         <is>
-          <t>99.107</t>
+          <t>97.5007</t>
         </is>
       </c>
       <c r="AR174" t="inlineStr">
         <is>
-          <t>0.3835</t>
+          <t>0.3594</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr">
         <is>
-          <t>0.1751</t>
+          <t>0.1074</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr">
         <is>
-          <t>0.2998</t>
+          <t>0.3006</t>
         </is>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>75.14</t>
+          <t>70.07</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>50.36</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>44.48</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>31.72</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>0.1386</t>
+          <t>0.1245</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>42.17</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="BD174" t="inlineStr">
         <is>
-          <t>0.3956</t>
+          <t>0.405</t>
         </is>
       </c>
       <c r="BE174" t="inlineStr">
         <is>
-          <t>0.1489</t>
+          <t>0.161</t>
         </is>
       </c>
       <c r="BF174" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>27.5</t>
         </is>
       </c>
       <c r="BG174" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH174" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI174" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ174" t="inlineStr"/>
@@ -49143,56 +49143,56 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-07-24T23:10:00Z</t>
+          <t>2026-07-24T20:10:00Z</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Shane McClanahan</t>
+          <t>Tomoyuki Sugano</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>663556</t>
+          <t>608372</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
@@ -49206,26 +49206,26 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Pitcher Vulnerable, Platoon Edge</t>
         </is>
       </c>
       <c r="P175" t="n">
-        <v>14.2</v>
+        <v>11.6</v>
       </c>
       <c r="Q175" t="n">
-        <v>42.1</v>
+        <v>73.2</v>
       </c>
       <c r="R175" t="n">
-        <v>41.1</v>
+        <v>43.1</v>
       </c>
       <c r="S175" t="n">
-        <v>94.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T175" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U175" t="n">
-        <v>34.2</v>
+        <v>24.9</v>
       </c>
       <c r="V175" t="inlineStr">
         <is>
@@ -49239,7 +49239,7 @@
       </c>
       <c r="X175" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y175" t="inlineStr">
@@ -49260,7 +49260,7 @@
       <c r="AB175" t="inlineStr"/>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD175" t="inlineStr"/>
@@ -49277,142 +49277,142 @@
       </c>
       <c r="AH175" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI175" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/31, 1 HR</t>
+          <t>Last 7 games: 4/14, 0 HR</t>
         </is>
       </c>
       <c r="AL175" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.9% barrel, 7.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 13.1% barrel, 22.5 HR allowed</t>
         </is>
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN175" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>33.19</t>
+          <t>27.73</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>86.95</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ175" t="inlineStr">
         <is>
-          <t>97.5007</t>
+          <t>97.0306</t>
         </is>
       </c>
       <c r="AR175" t="inlineStr">
         <is>
-          <t>0.3594</t>
+          <t>0.3015</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr">
         <is>
-          <t>0.1074</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT175" t="inlineStr">
         <is>
-          <t>0.3006</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>70.07</t>
+          <t>69.94</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>44.48</t>
+          <t>34.69</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>26.72</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>0.1245</t>
+          <t>0.1056</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>43.02</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="BD175" t="inlineStr">
         <is>
-          <t>0.405</t>
+          <t>0.5492</t>
         </is>
       </c>
       <c r="BE175" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>0.2448</t>
         </is>
       </c>
       <c r="BF175" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="BG175" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH175" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI175" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ175" t="inlineStr"/>
@@ -63415,32 +63415,32 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>695720</t>
+          <t>687859</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Tommy White</t>
+          <t>Troy Johnston</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>2026-07-25T00:10:00Z</t>
+          <t>2026-07-24T20:10:00Z</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -63450,17 +63450,17 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Zebby Matthews</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>805673</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L226" t="n">
@@ -63478,65 +63478,61 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P226" t="n">
-        <v>11.2</v>
+        <v>24.6</v>
       </c>
       <c r="Q226" t="n">
-        <v>57.4</v>
+        <v>32.6</v>
       </c>
       <c r="R226" t="n">
-        <v>27.1</v>
+        <v>43.1</v>
       </c>
       <c r="S226" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T226" t="n">
         <v>50</v>
       </c>
       <c r="U226" t="n">
-        <v>37.3</v>
+        <v>7</v>
       </c>
       <c r="V226" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W226" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X226" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y226" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z226" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB226" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr"/>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD226" t="inlineStr"/>
@@ -63548,17 +63544,17 @@
       </c>
       <c r="AG226" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI226" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ226" t="inlineStr">
@@ -63568,12 +63564,12 @@
       </c>
       <c r="AK226" t="inlineStr">
         <is>
-          <t>Contact streak: 7/19 over last 5 games</t>
+          <t>Last 7 games: 3/18, 0 HR</t>
         </is>
       </c>
       <c r="AL226" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.8% barrel, 14.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM226" t="inlineStr">
@@ -63583,104 +63579,112 @@
       </c>
       <c r="AN226" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>89.74</t>
         </is>
       </c>
       <c r="AQ226" t="inlineStr">
         <is>
-          <t>95.2823</t>
+          <t>99.1025</t>
         </is>
       </c>
       <c r="AR226" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>0.4034</t>
         </is>
       </c>
       <c r="AS226" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>0.1268</t>
         </is>
       </c>
       <c r="AT226" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>70.32</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>23.23</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>0.122</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>11.79</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>90.11</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="BD226" t="inlineStr">
         <is>
-          <t>0.4554</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="BE226" t="inlineStr">
         <is>
-          <t>0.1956</t>
+          <t>0.121</t>
         </is>
       </c>
       <c r="BF226" t="inlineStr">
         <is>
-          <t>29.27</t>
-        </is>
-      </c>
-      <c r="BG226" t="inlineStr"/>
-      <c r="BH226" t="inlineStr"/>
+          <t>27.6</t>
+        </is>
+      </c>
+      <c r="BG226" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH226" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI226" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ226" t="inlineStr"/>
@@ -63691,56 +63695,56 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>669707</t>
+          <t>695720</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Jared Triolo</t>
+          <t>Tommy White</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2026-07-24T22:40:00Z</t>
+          <t>2026-07-25T00:10:00Z</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Matthew Boyd</t>
+          <t>Zebby Matthews</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>571510</t>
+          <t>805673</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L227" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="M227" t="inlineStr">
         <is>
@@ -63754,26 +63758,26 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P227" t="n">
-        <v>16.7</v>
+        <v>11.2</v>
       </c>
       <c r="Q227" t="n">
-        <v>48.3</v>
+        <v>57.4</v>
       </c>
       <c r="R227" t="n">
-        <v>38.8</v>
+        <v>27.1</v>
       </c>
       <c r="S227" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T227" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U227" t="n">
-        <v>43.4</v>
+        <v>37.3</v>
       </c>
       <c r="V227" t="inlineStr">
         <is>
@@ -63787,7 +63791,7 @@
       </c>
       <c r="X227" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y227" t="inlineStr">
@@ -63812,7 +63816,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD227" t="inlineStr"/>
@@ -63824,17 +63828,17 @@
       </c>
       <c r="AG227" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH227" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AH227" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="AI227" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ227" t="inlineStr">
@@ -63844,12 +63848,12 @@
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>Contact streak: 9/22 over last 7 games</t>
+          <t>Contact streak: 7/19 over last 5 games</t>
         </is>
       </c>
       <c r="AL227" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.8% barrel, 9.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.8% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM227" t="inlineStr">
@@ -63859,112 +63863,104 @@
       </c>
       <c r="AN227" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AQ227" t="inlineStr">
         <is>
-          <t>98.6412</t>
+          <t>95.2823</t>
         </is>
       </c>
       <c r="AR227" t="inlineStr">
         <is>
-          <t>0.3347</t>
+          <t>0.402</t>
         </is>
       </c>
       <c r="AS227" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>0.077</t>
         </is>
       </c>
       <c r="AT227" t="inlineStr">
         <is>
-          <t>0.2911</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>70.97</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>0.0891</t>
+          <t>0.053</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>11.79</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>43.11</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>89.55</t>
+          <t>90.11</t>
         </is>
       </c>
       <c r="BD227" t="inlineStr">
         <is>
-          <t>0.4281</t>
+          <t>0.4554</t>
         </is>
       </c>
       <c r="BE227" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>0.1956</t>
         </is>
       </c>
       <c r="BF227" t="inlineStr">
         <is>
-          <t>24.73</t>
-        </is>
-      </c>
-      <c r="BG227" t="inlineStr">
-        <is>
-          <t>In From RF</t>
-        </is>
-      </c>
-      <c r="BH227" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
+          <t>29.27</t>
+        </is>
+      </c>
+      <c r="BG227" t="inlineStr"/>
+      <c r="BH227" t="inlineStr"/>
       <c r="BI227" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ227" t="inlineStr"/>
@@ -63975,27 +63971,27 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>593428</t>
+          <t>669707</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Xander Bogaerts</t>
+          <t>Jared Triolo</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>2026-07-24T23:10:00Z</t>
+          <t>2026-07-24T22:40:00Z</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -64005,22 +64001,22 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Ryan Gusto</t>
+          <t>Matthew Boyd</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>687473</t>
+          <t>571510</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L228" t="n">
@@ -64038,58 +64034,62 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P228" t="n">
-        <v>27.2</v>
+        <v>16.7</v>
       </c>
       <c r="Q228" t="n">
-        <v>47.6</v>
+        <v>48.3</v>
       </c>
       <c r="R228" t="n">
-        <v>35</v>
+        <v>38.8</v>
       </c>
       <c r="S228" t="n">
-        <v>52.4</v>
+        <v>40.2</v>
       </c>
       <c r="T228" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U228" t="n">
-        <v>6</v>
+        <v>43.4</v>
       </c>
       <c r="V228" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W228" t="inlineStr">
+      <c r="Z228" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X228" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y228" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z228" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB228" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC228" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -64109,12 +64109,12 @@
       </c>
       <c r="AH228" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI228" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ228" t="inlineStr">
@@ -64124,12 +64124,12 @@
       </c>
       <c r="AK228" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 0 HR</t>
+          <t>Contact streak: 9/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL228" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.2% barrel, 7.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.8% barrel, 9.9 HR allowed</t>
         </is>
       </c>
       <c r="AM228" t="inlineStr">
@@ -64139,112 +64139,112 @@
       </c>
       <c r="AN228" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>38.78</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="AQ228" t="inlineStr">
         <is>
-          <t>99.7175</t>
+          <t>98.6412</t>
         </is>
       </c>
       <c r="AR228" t="inlineStr">
         <is>
-          <t>0.3836</t>
+          <t>0.3347</t>
         </is>
       </c>
       <c r="AS228" t="inlineStr">
         <is>
-          <t>0.1348</t>
+          <t>0.095</t>
         </is>
       </c>
       <c r="AT228" t="inlineStr">
         <is>
-          <t>0.3186</t>
+          <t>0.2911</t>
         </is>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>72.34</t>
+          <t>70.97</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>27.68</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>44.64</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>23.69</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>0.1126</t>
+          <t>0.0891</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>43.39</t>
+          <t>43.11</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>89.83</t>
+          <t>89.55</t>
         </is>
       </c>
       <c r="BD228" t="inlineStr">
         <is>
-          <t>0.4285</t>
+          <t>0.4281</t>
         </is>
       </c>
       <c r="BE228" t="inlineStr">
         <is>
-          <t>0.1676</t>
+          <t>0.172</t>
         </is>
       </c>
       <c r="BF228" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>24.73</t>
         </is>
       </c>
       <c r="BG228" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH228" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI228" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ228" t="inlineStr"/>
@@ -64255,56 +64255,56 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>687859</t>
+          <t>593428</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Troy Johnston</t>
+          <t>Xander Bogaerts</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>2026-07-24T20:10:00Z</t>
+          <t>2026-07-24T23:10:00Z</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Ryan Gusto</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>687473</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L229" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="M229" t="inlineStr">
         <is>
@@ -64322,22 +64322,22 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>24.6</v>
+        <v>27.2</v>
       </c>
       <c r="Q229" t="n">
-        <v>32.6</v>
+        <v>47.6</v>
       </c>
       <c r="R229" t="n">
-        <v>43.1</v>
+        <v>35</v>
       </c>
       <c r="S229" t="n">
-        <v>76.2</v>
+        <v>52.4</v>
       </c>
       <c r="T229" t="n">
         <v>50</v>
       </c>
       <c r="U229" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="V229" t="inlineStr">
         <is>
@@ -64351,7 +64351,7 @@
       </c>
       <c r="X229" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y229" t="inlineStr">
@@ -64372,7 +64372,7 @@
       <c r="AB229" t="inlineStr"/>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD229" t="inlineStr"/>
@@ -64389,12 +64389,12 @@
       </c>
       <c r="AH229" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI229" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ229" t="inlineStr">
@@ -64404,12 +64404,12 @@
       </c>
       <c r="AK229" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Last 7 games: 4/25, 0 HR</t>
         </is>
       </c>
       <c r="AL229" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 6.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.2% barrel, 7.2 HR allowed</t>
         </is>
       </c>
       <c r="AM229" t="inlineStr">
@@ -64419,112 +64419,112 @@
       </c>
       <c r="AN229" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.78</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>89.74</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AQ229" t="inlineStr">
         <is>
-          <t>99.1025</t>
+          <t>99.7175</t>
         </is>
       </c>
       <c r="AR229" t="inlineStr">
         <is>
-          <t>0.4034</t>
+          <t>0.3836</t>
         </is>
       </c>
       <c r="AS229" t="inlineStr">
         <is>
-          <t>0.1268</t>
+          <t>0.1348</t>
         </is>
       </c>
       <c r="AT229" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3186</t>
         </is>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>70.32</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>27.68</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>44.64</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>23.69</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.1126</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>9.22</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>43.39</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>89.83</t>
         </is>
       </c>
       <c r="BD229" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.4285</t>
         </is>
       </c>
       <c r="BE229" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>0.1676</t>
         </is>
       </c>
       <c r="BF229" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="BG229" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH229" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI229" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ229" t="inlineStr"/>
@@ -65505,12 +65505,12 @@
       </c>
       <c r="AH233" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI233" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ233" t="inlineStr">
@@ -65520,7 +65520,7 @@
       </c>
       <c r="AK233" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 1/18, 0 HR</t>
         </is>
       </c>
       <c r="AL233" t="inlineStr">
@@ -69616,7 +69616,7 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>34</v>
+        <v>34.1</v>
       </c>
       <c r="M248" t="inlineStr">
         <is>
@@ -69649,7 +69649,7 @@
         <v>78</v>
       </c>
       <c r="U248" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="V248" t="inlineStr">
         <is>
@@ -69706,7 +69706,7 @@
       </c>
       <c r="AI248" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ248" t="inlineStr">
@@ -69716,7 +69716,7 @@
       </c>
       <c r="AK248" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/26, 0 HR</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL248" t="inlineStr">
@@ -79722,7 +79722,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>60.9</v>
+        <v>61</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -79755,7 +79755,7 @@
         <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>28.2</v>
+        <v>29.7</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -79807,12 +79807,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -79822,7 +79822,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 0 HR</t>
+          <t>Last 7 games: 7/22, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -80233,12 +80233,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -80263,7 +80263,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -80282,11 +80282,11 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>60.2</v>
+        <v>60</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Longshot</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -80296,11 +80296,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Strong Barrel, Pitcher Vulnerable, Premium Lineup Spot</t>
+          <t>Strong Barrel, Pitcher Vulnerable, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>51.1</v>
+        <v>59.8</v>
       </c>
       <c r="Q15" t="n">
         <v>73.2</v>
@@ -80309,13 +80309,13 @@
         <v>43.1</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>64.3</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>16.6</v>
+        <v>0</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -80329,7 +80329,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -80367,12 +80367,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -80382,82 +80382,82 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 1/18, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 13.1% barrel, 22.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 13.1% barrel, 22.5 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>lift-pull EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>13.63</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>45.31</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>91.33</t>
+          <t>92.26</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>102.186</t>
+          <t>103.1979</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4498</t>
+          <t>0.4598</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.2014</t>
+          <t>0.2153</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3238</t>
+          <t>0.3554</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>74.46</t>
+          <t>76.71</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>71.12</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>33.18</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>28.22</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1965</t>
+          <t>0.2074</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -80513,12 +80513,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -80543,7 +80543,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -80562,7 +80562,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>60</v>
+        <v>59.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -80576,11 +80576,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Strong Barrel, Pitcher Vulnerable, Platoon Edge</t>
+          <t>Strong Barrel, Pitcher Vulnerable, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>59.8</v>
+        <v>51.1</v>
       </c>
       <c r="Q16" t="n">
         <v>73.2</v>
@@ -80589,13 +80589,13 @@
         <v>43.1</v>
       </c>
       <c r="S16" t="n">
-        <v>64.3</v>
+        <v>100</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -80609,7 +80609,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -80647,7 +80647,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -80662,82 +80662,82 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 13.1% barrel, 22.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 13.1% barrel, 22.5 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>13.63</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>45.31</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>92.26</t>
+          <t>91.33</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>103.1979</t>
+          <t>102.186</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4598</t>
+          <t>0.4498</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.2153</t>
+          <t>0.2014</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3554</t>
+          <t>0.3238</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>76.71</t>
+          <t>74.46</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>71.12</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>33.18</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>28.22</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.2074</t>
+          <t>0.1965</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -81122,7 +81122,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>59.4</v>
+        <v>59.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -81155,7 +81155,7 @@
         <v>78</v>
       </c>
       <c r="U18" t="n">
-        <v>87</v>
+        <v>93.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -81212,7 +81212,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
